--- a/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:18</t>
+    <t xml:space="preserve">2026-09-09 21:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:04</t>
+    <t xml:space="preserve">2026-09-17 13:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_i_peringrmin_a_2022.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:56</t>
+    <t xml:space="preserve">2026-10-05 18:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
